--- a/tests/fixtures/modeles/Modele_Controle_Laitier.xlsx
+++ b/tests/fixtures/modeles/Modele_Controle_Laitier.xlsx
@@ -57,7 +57,7 @@
     <t>Contrôle 3 (mL[/code])</t>
   </si>
   <si>
-    <t>180055</t>
+    <t>250101</t>
   </si>
   <si>
     <t>1440</t>
@@ -69,7 +69,7 @@
     <t>1060</t>
   </si>
   <si>
-    <t>180133</t>
+    <t>250102</t>
   </si>
   <si>
     <t>1620/01</t>
@@ -81,7 +81,7 @@
     <t>840</t>
   </si>
   <si>
-    <t>190059</t>
+    <t>250103</t>
   </si>
   <si>
     <t>09</t>
@@ -90,7 +90,7 @@
     <t>1200</t>
   </si>
   <si>
-    <t>190069</t>
+    <t>250104</t>
   </si>
   <si>
     <t>07</t>
@@ -102,7 +102,7 @@
     <t>900</t>
   </si>
   <si>
-    <t>190085</t>
+    <t>250105</t>
   </si>
   <si>
     <t>1460/08</t>
